--- a/text/foundationScores/milkywaysynonyms_6_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/milkywaysynonyms_6_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>33.147</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21.175</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>81.69999999999999</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>6.3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>-27.48</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin took a deep breath and tried to calm down.  The situation was almost desperate, and after Martin spent most of the last weeks drunk, he knew it was time to face reality.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.04710464652736692</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.02560354374307863</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.001265822784810127</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.08976789112273428</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.1093529973362362</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.04314526047786917</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.06407739355107131</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.07857007930937243</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.06177803469268849</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.05039929112753651</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.02145821543105075</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.02374881404174573</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.1075418604436407</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.0681226530905031</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.04487145797748873</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.101993991325052</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1492463512588907</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.1439752342102659</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>0.1061771530368336</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.0406200523687736</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>0.05807701531116279</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>0.06033789994338105</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1.285714285714286</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>46.9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>34.308</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>73.2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>26.8</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>-85.91</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin looked at the reflection in the mirror and started weeping uncontrollably.  That evening, at the utmost moment of hopelessness, Martin did the inconceivable, calling his mom to talk.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.02481995884773662</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.01618122977346278</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.03400956622134257</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.026956111201903</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.02275008028259473</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.07074883872630054</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.03957177909602923</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.05886742401231193</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.04943578236901567</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.06851170021273113</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.6</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.02302631578947368</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.05898550724637681</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.09004112808460635</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.03894261088921589</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.04042372881355932</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.09723372435160467</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.07444444444444445</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.08313291646624979</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.1359053335890787</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.06256759679861562</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.0452449947312961</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.1053425086766637</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -804,104 +834,114 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>64.951</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>48.261</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>73</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>22.2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>4.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>-86.87</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">  In general...  Help from his mom resembled a lengthy and very excruciating lecture about all the things he had done wrong in his life, starting from how Martin struggled to remain in his mom's belly up to how Martin had messed up everything with Sophia Jones.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0382219338092148</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.01773868991933349</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.04331519694771561</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.03995162342130516</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.03307262797644213</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.06836299140749033</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.04885146062999605</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.05145566549254765</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0298150604185087</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.07431424829630159</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.09017422944911029</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.1171251703030978</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.04930146377617195</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.1020059978594212</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.1056966682330281</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.1214466914701519</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>0.02122914994202123</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>0.1391251363812339</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.05725268226746642</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.122693179836037</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.07672493841808638</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.1147566718995291</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.02804232804232804</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.0469760391973704</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.5384615384615384</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>73.341</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>66.573</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>64.60000000000001</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>14.1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>21.3</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>22.63</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">  To be honest, it wasn't far from the truth.  His mom had gone through nearly 30 hours of agonizing labor.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.03910189075630251</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.06035197311951916</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.03340024534403926</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.04144693473961767</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.04116896013618953</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.04021568846845106</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.03909426790757724</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.06191034103269999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.02305650355414321</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0447745863159397</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>3.5</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>0.0958100558659218</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.04462279293739968</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.07538239538239538</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.08700066558436978</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.04017857142857143</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>0.1871816100878133</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.07846693657219973</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.05818429936076994</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.06686869652274988</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.04770887007729113</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.0032</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.0568222844693433</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>1.25</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>87.05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>73.701</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>75.8</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>24.2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>91.03</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin could imagine, though he never really tried, it could have gone easier.  But to this day, each time Martin looked at his mom's belly, he felt that it was the only time he really felt protected and loved.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0381119721774915</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.04196991330451642</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.04710666860583296</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.03991297325243359</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.03024957233626588</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.06477081346667903</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.03613810003283537</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0568870032748888</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.01824523896695608</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.05590140503566963</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.1409621578099839</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.1300237123983125</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.05040045178453482</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.0587810449590136</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.08243031184858925</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.1284518716461037</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.07576923950314508</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.08158411769281693</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.04612654320987655</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.06700966976829045</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.07602446129473328</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.0927987638406014</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.01532567049808429</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.05510573271309468</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>1.285714285714286</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>108.574</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88.952</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>3.2</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>10.9</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>44.04</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">  As for Sophia, it wasn't that simple, as nothing in life ever is.  Martin had treated her badly sometimes, and well, Martin did take Sophia for granted, although Sophia was better than anything Martin could ever hope for, and Martin could go on and on and on about all the things that ended poorly, but it was beside the point.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.02293790546802595</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.05125939777364066</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.0458035665245776</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.06314024686869514</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.05864435551311536</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.08324069934118908</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.08520508553327547</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.03125372778241679</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.0500070670714049</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.03937871142936965</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>0.8</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.09194549082453318</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1125913517167387</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.05153162055335968</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.08580162519621029</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.09206916785858363</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.08731341018062171</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.05119819945704247</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.0767681154282473</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.08434221686531851</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.09538412975912976</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.06507127886086898</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.05360653235653236</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.03225334448160536</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.04178725369458128</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>116.815</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>109.381</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin learned the lesson, or so he told everybody, not understanding what the lesson was and how the heck was he supposed to learn it.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.1022875816993464</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.0616800920598389</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.07703997248297026</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0698237664248739</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.02316593161663584</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.03868796898250568</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.04901666781996356</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.02543005517689062</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.01701002446917673</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.08904964950046919</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>1.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.1434027777777778</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.1584991447052551</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.08377836226154689</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.02941176470588236</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.1052345807146015</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.1462304955938233</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.05944207583551846</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.03933963288801998</v>
       </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.1230044828608147</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.1194444444444445</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.03166035353535353</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.03950617283950617</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>124.71</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>118.498</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>86.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>13.3</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>-38.18</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin's mom identified his usual habit and spoke to him, annoyed.  I'm so fed up with you, Martin.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.05927579365079365</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.01571277375234063</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.02738095238095238</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.02328392517438174</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.004716981132075472</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.04041720990873533</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.06666781959048146</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.04329004329004329</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>0.8</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.04</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0.015625</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0.01063829787234043</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.1547008547008547</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.07039128680919726</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.1414728682170543</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.1222222222222222</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>132.385</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>125.291</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>79.10000000000001</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>20.9</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>-67.56999999999999</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Listen to me.  This might sound a bit crazy, but have you explored the idea of seeing a healer about your painful breakup?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.06352142764662724</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.04510624207326729</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.03342895241083334</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.04772789115646259</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.02523736767434246</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.03650020614306328</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.05893569213241345</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.02258852258852259</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.03137379436702028</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.07184107655833818</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.08789070296594946</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.2259692513368984</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.08541666666666667</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.111394783377542</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.06178396072013093</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.0503441461087638</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.05219780219780219</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
       <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.09036796536796537</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0.0108695652173913</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>140.151</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>133.242</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>45</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>23.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>30.45</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Wow, Mom, that was just a dumb idea.  I'm not that desperate.  Dearest, I wish you weren't.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.08448623470522804</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.05273752012882447</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.04359705393205036</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.04943096119566708</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.0078125</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03469995419147962</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.03435534591194969</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.05915178571428571</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.1840659340659341</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.2794117647058824</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.1428944618599791</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.07894736842105263</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.03296703296703297</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
       <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.09740259740259741</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>152.486</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>141.492</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>80.60000000000001</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>13.1</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>6.3</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>-32.91</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin sometimes hated his mother for her harsh candor, but she had a point.  Fine, Mom, I'll check it out, Martin said dispassionately while he hung up and mumbled to himself.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.022493961352657</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>0.0339094241113441</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.134826340302289</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.07939410205085308</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.07163266298664979</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.05899184161318625</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.08331580824165842</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.75</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.03759398496240601</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.025</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0.03165867480383609</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.1060228599738137</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.08898260127040253</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.07129703090307046</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.09739049990650994</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.09919337865069486</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.2051484744984577</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.03292759051186017</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1749,104 +1869,114 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>163.439</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>153.327</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>73.2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>14</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>12.8</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>15.31</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">  What do I have to lose?  Martin woke up at dawn the next morning and anxiously scanned the internet for the combination of best and inexpensive Healer.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.03100775193798449</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.02185792349726776</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.09445100354191265</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.09045893719806763</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.09173933032548642</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.0746996996996997</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.07460738495221254</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
         <v>0.1627906976744186</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>0.2246503496503497</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.2525987525987526</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170.414</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>164.22</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>77.2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>5.7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>17.1</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>58.59</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Before long, Martin understood that knowing nothing about the subject, it was hard to figure out which Healer was the best.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.02811584403876493</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.05964213754137709</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0483124908585637</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.06154616017184733</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.04640023315282791</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.05500509911868526</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.07987952217279405</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06390556255718637</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.1047248803827751</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.08732558139534885</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.1087914023960536</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1090025457070123</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.05965532479010163</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.09166022419791264</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.1615316316118627</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.09785289424053387</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.06419457735247208</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.1035137701804368</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.0297661233167966</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1959,67 +2099,71 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>179.791</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>171.256</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>11.6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>44.04</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  He would have to compromise for the most inexpensive one he could get.  Andre the Giant, hypnosis and physio specialist, customer satisfaction guaranteed.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.04347826086956521</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.125</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.0925925925925926</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.04</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.1206395348837209</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.25</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
@@ -2057,6 +2201,12 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>188.623</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>180.092</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>70.89999999999999</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>4.6</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>24.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>82.91</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The combination was kind of strange, but just thinking about The Princess Bride, which was Martin's all-time favorite film by far, made the choice much more easy.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.02148846960167715</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.0671963412607624</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.05818483360121537</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.06038997495106454</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.03774165183225794</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.03691830887976722</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.02633141153032589</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.03084066996183432</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.03551791629027401</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.03047180716535555</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>2.25</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.02881183069862315</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1200110422335328</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.06318939560843063</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.0891338204778233</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.09229424013477171</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.1323803860853844</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.01904761904761905</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.09872979633253605</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.08128458918688804</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.05452744765138653</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.06161230074273553</v>
       </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0.05395965504152059</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>196.595</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>188.664</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>63.6</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>13.1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>23.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>34</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  A deep voice answered Martin's call.  Today's your lucky day, Mr. Williams.  Somehow a fake name felt comforting.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.02285714285714285</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.0161764705882353</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.04742625795257373</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.01900223380491437</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.07037225253393069</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.09824993595772666</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.04582317073170732</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.07725193761101688</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.05867660362828617</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0859375</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.05696202531645569</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.0824319855461724</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.02706109134045077</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.07391347391347391</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.01393316983445739</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.1451292851292851</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.09503359533468561</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AD17" t="n">
         <v>0.05357142857142857</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>0.112769961334333</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.09419221698113207</v>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.04629629629629629</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>203.344</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>197.296</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>14.4</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>52.16</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve"> I have a place at 1.30 p.m. today, but it's going to be cold, so be sure to bring a coat.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.02521739130434782</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.04420216703681271</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.0477952903649498</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.03416879795396419</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.03125268817204301</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.08967975356128602</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.04549406532165153</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.04494432071269489</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.04201505476231843</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.04847513651127308</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.09099225139905295</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.06901647286821705</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.1085714285714286</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.1901795363581596</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.1226604167902797</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.03600464576074332</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>0.08451342471961029</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.1069096481876333</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.08579770967532045</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.1036579075130477</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
       <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.05666746612303633</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2379,67 +2559,71 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>213.722</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>204.809</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>13.1</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>9</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>-25</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> Martin arrived at Andre's clinic at 1.27, and Andre, that to Martin's dissatisfaction was a surprisingly small man, invited him in.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.04163059163059164</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.03703235591506572</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.03475274725274725</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.1046679166366193</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.05638769984965353</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.05796145164090989</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.03791469194312796</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.05431939528466015</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -2447,36 +2631,42 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.0772520716385993</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
       <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0.1534127289025483</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.1943609765043627</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.1209620253164557</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.1373400579060428</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.05376344086021505</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.06517094017094016</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.110019825177976</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>221.974</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>213.742</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>74.8</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>25.2</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>-65.97</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  I dislike Thursdays, Andre said.  For some reason, everyone seems to be ill.  I know what you mean.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.01285500747384155</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.05238776511993785</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.0228831663170978</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.01194029850746268</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.05971870279405276</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.07198582249949445</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.01095890410958904</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.0277961644904985</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.05897334753470259</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.03855577047066409</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>0.03747899159663866</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.05545709549917124</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>0.02555410691003911</v>
       </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.08426311350986675</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.09094815810892105</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.06143521454238005</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.07617861445168141</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.04649772821467044</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.1197877022840204</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.01095100864553314</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.08011389295149503</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>228.083</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>221.994</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>8.6</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>12.8</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve"> I used to be in the bathroom tissue industry, Martin replied, feeling that was an unconventional response.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.01037613488975357</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.01298701298701299</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.03196111326192626</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>0.03336940836940837</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.1748818060576808</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.05558808222742648</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.06049783549783549</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.01510757332675141</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.1326694139194139</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.0429042904290429</v>
       </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0.108065953654189</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
       <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>0.1646903820816864</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>0.165510153010153</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>0.08957002979991487</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>0.1050559926964421</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>0.07317073170731707</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>0.099822695035461</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.09026754026754026</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>234.404</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>228.232</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>14.4</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>40.19</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">  So, are you interested in physio work, or you came here only for hypnosis session?  Andre asked.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.07739009581337727</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.06050796888999409</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.07273069466215659</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.05739156268568033</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.047600624024961</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.01132075471698113</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.0145985401459854</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.01316455696202532</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.01351981351981352</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.02344332284091321</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.02365591397849462</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.07575757575757576</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.1164704756436022</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.1012423816221285</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.09752791068580542</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.1066781691828421</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.03615819209039548</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.1526531516561427</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.06331310487069648</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AD22" t="n">
         <v>0.02142857142857143</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>0.04065040650406504</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.04285714285714285</v>
       </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>0.06538461538461539</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2799,67 +3019,71 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>241.938</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>235.366</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>52.6</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>47.4</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>91</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  Just the hypnosis, please.  My neck seems to be just perfect these days, thank you.  Martin replied confidently.  Okay, dude.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.01515151515151515</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.07554945054945056</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.03030303030303031</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>0.25</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
@@ -2870,33 +3094,39 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.0625</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.28</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -2904,67 +3134,71 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>251.815</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>242.7</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>73.2</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>17.1</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>42.15</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  Andre replied and coughed.  What seems to be worrying you, Mr. Williams?  It's Sophia, the best girl on planet Earth.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.05405405405405405</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.02325581395348838</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.02325581395348838</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.06398809523809523</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.1430833761342236</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.1030564263322884</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.01878306878306878</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.04665704665704665</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.0187793427230047</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.375</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
@@ -3002,6 +3236,12 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>261.085</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>252.556</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>74.7</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>20.6</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4.7</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>-70.92</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  I can't stop thinking of her.  The wedding was supposed to happen in the summer, but I was scared to marry.  I'm totally obsessed with Sophia.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.02441742654508612</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.04628704628704628</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.03225230054498347</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.08808242475153223</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.07670091974628802</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.0464418733809485</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.08198704630743466</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1011355047069333</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>1.75</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.08481532147742818</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1012059973924381</v>
       </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.05</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.05300366504809213</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0.1645502694323466</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AC25" t="n">
         <v>0.0816614420062696</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
         <v>0.08297413793103448</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.1560724821893733</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.117287784679089</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>0.02906976744186046</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>0.1195671603677222</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.5714285714285714</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>271.116</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>261.826</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>82.5</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>17.5</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>64.86</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">  I dream about Sophia constantly, and I see her image in practically every woman I meet.  To be honest, you are the 30th counselor I've spoken to.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.04024797369120382</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.07623142991876621</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0553448770186571</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.02172949002217295</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.03650365806700039</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.03944874163608698</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.04731831757093081</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.02549565840705081</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.08433038387524143</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.06721962394887389</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.06111111111111111</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
         <v>0.06878306878306878</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.1837962962962963</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.02164502164502164</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.08641975308641975</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.1257802180220363</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.1097373737373737</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.09214340198321891</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.1179332715477294</v>
       </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
         <v>0.1407241508025383</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>283.083</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>271.156</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>11.1</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>38.55</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Do you enjoy candy, Mr. Williams?  Martin didn't understand the relevance of the question, though he replied nevertheless, I'm not crazy about it, but I eat a little now and then.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.06546822342790219</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.06280709924968898</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.04347679057016498</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.04685033581137477</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.05473199591701202</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0829670027142313</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.02135642135642136</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.01734846862283144</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.06835057821059039</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>1.4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.0274914089347079</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.07301587301587302</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.04883710548636222</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.1025354213273676</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.04970760233918128</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.08511801402019421</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.08055555555555556</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.03300330033003301</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.0430172068827531</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05720245937637242</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>292.135</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>283.143</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>89.3</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>10.7</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>45.88</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve"> Just keep your eyes on the Kit Kat, Andre replied, while he started to gently swing a small Kit Kat that was dangling from a cord.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>0.03509136212624585</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.1198298460480229</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0684896433945065</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.07725977725977726</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.04557673509286413</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.04405818979763694</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.1066666666666667</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>0.05426356589147287</v>
       </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0.02298850574712644</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.1502675819374584</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.03184713375796178</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.08358847736625515</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.05805656307043122</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.1144049187527448</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
         <v>0.06353178784685633</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>0.09677595628415302</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>303.21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>293.657</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>75.5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>7.9</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>16.5</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>34</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aren't you supposed to do that with a pocket clock?  Martin asked doubtfully.  Put your faith in Andre, and everything will be just fine.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.2406609195402299</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.129870177283215</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.1544871794871795</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.04791666666666667</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.06300813008130081</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.01415094339622642</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.02848101265822785</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.01645569620253165</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.03191747572815534</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.08490650915349711</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.08730158730158731</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.1875968992248062</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.3715493352976253</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.04857226964969091</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.1654320987654321</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.1334581961733954</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.1083773768300832</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.03490401396160558</v>
       </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>0.03418803418803418</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.04285714285714285</v>
       </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0.08717948717948719</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>313.372</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>303.494</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>66.3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>8.1</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>25.7</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>65.71000000000001</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin took a deep breath and tried not to laugh.  The next thing Martin remembered was slowly awakening and feeling like he could certainly use a good physio session.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.02416372728018449</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.02549071421147437</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.06170598689980109</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.04421968348130027</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.03428409138906592</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.07940583606383064</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.05644997073886064</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.03548973189930636</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0.03787414642521811</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.03633041779820836</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>1.25</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.07070148708236623</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.06674904609421134</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.0510149423892114</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.05097275112767761</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.1037470065706497</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.05759716191831052</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.04291544180870915</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>0.09706864977949316</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.08608632023122302</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.1014993513344338</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.08571414027042376</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.02840608465608465</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.05674859742747673</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.06306231651409316</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>320.581</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>313.992</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>33.6</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>84.42</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  When Martin exited Andre's clinic an hour later, he felt happier than he felt for years.  It was like a blessing.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.001954887218045113</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.0544496349794279</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.002966958867161159</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.001299638989169675</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0.00242914979757085</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.07293111370895992</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.00743801652892562</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.06817761806981519</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.04238735580906252</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.06010481261091973</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.1585702705055385</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>0.09545817738340552</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.04810929810929811</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.01243445208945742</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.02026228563193544</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.04086008479709267</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>0.00955831608005521</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.04137931034482759</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.01717791411042945</v>
       </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
         <v>0.0810126582278481</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.1279726478409522</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.01166666666666667</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.009448818897637795</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>335.34</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>321.402</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>78.7</v>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>21.3</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>84.81</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin's neck was relaxed, plus he felt rising optimism in his soul.  As he walked down the street, Martin noticed a woman that appeared exactly like Sophia, though after a second, he understood that he was fantasizing.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.008140722175809894</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.04511987252384445</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.02890394957950056</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.06072699696630948</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.01968522455659759</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.07798694006105487</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.01830665979112855</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.0615631291603235</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.02901882050799412</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.04041658213295463</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>0.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.05598979787993628</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.06848016899455474</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.02012843123954235</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.01543521520138409</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.05958230067652307</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.05953358394303276</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.02387438916424424</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.1469915345826853</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.05140506868645781</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.09262232973997681</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.1246566262222491</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.08998840062718218</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.03087395696091348</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.02929056085623604</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>346.978</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>335.641</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>80.5</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>13.6</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>36.12</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Feeling good, he stopped to purchase a Kit Kat and continued walking home unburdened.  As days went by, Martin noticed that he was thinking about Sophia less and less.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.01232207350754196</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.0384327485380117</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.009325396825396825</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.02567673947324108</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.04975275624243176</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.07678516219531101</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.05766832320721798</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.06489201727675195</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.06106565654270726</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.03851579176150496</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>1.285714285714286</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.05461950696677385</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.07216374765394373</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.04531077388220246</v>
       </c>
-      <c r="V33" t="n">
+      <c r="X33" t="n">
         <v>0.02368987796123475</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.06382601607908826</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.0774201488984865</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.04693384202996267</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.1373609512850019</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.1052861834128988</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.08801430917194464</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.1402493218683339</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.08254645141638743</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AG33" t="n">
         <v>0.04642857142857143</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>0.07772893005738159</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>0.7777777777777778</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>355.692</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>347.419</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>82.5</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>17.5</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>59.65000000000001</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  He really felt prepared to see Sophia.  Martin called Sophia's cell and finally convinced her to come with him to the pub the next day.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.05710284805972926</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.04870785451376194</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.03068571565762577</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.04271813971549258</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.02320537735660048</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.06282657341499308</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0455183966087513</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.05393540274296853</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.03604672429997544</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.02659801266111625</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.1259868421052632</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.1039783001808318</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.1033972067896596</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.07274695592522724</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.08561312085124381</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.0627359819667512</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.03220531887583643</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.06415397798097668</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.05763664207813144</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.04613339588709047</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.07652421982127765</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.06372985666855616</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.02985965959988056</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.01601905857225006</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -4059,67 +4399,71 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>362.196</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>355.732</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>100</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  When Martin arrived at the pub, Sophia was staring at the clock.  How are you doing, Sophia?</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.1025641025641026</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>0.08080808080808081</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>0.01470588235294117</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
@@ -4127,36 +4471,42 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
       <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
         <v>0.125</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
       <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.07407407407407407</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>369.645</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>362.236</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>76.3</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>13.9</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>-23.02</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  he inquired, without losing control over his voice this once.  I could be worse.  How are you these days?</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.03809523809523809</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>0.04273504273504273</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0.0597090449082859</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.09563375692407949</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.1164371006094076</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.08141269098035135</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.128931969351168</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.05952380952380953</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.08080808080808081</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.0998565151107524</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.3542923402223586</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.203956072529271</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.07373737373737374</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.1352813852813853</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.1303680981595092</v>
       </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.1909424872026498</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>377.173</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>370.746</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>70.19999999999999</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>29.8</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>73.50999999999999</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  Feeling better, he replied, actually believing that the response he made was true.  I have to go to the bathroom.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.02752860953364309</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.04161100171784074</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.02995325422509889</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.04995413196115966</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.05024704550021006</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.1123729970372439</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.04765157429091855</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.0604978354978355</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.01510757332675141</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.05063965884861407</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.02403846153846154</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.08572731418148655</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.06112409896746542</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.1225283362290064</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.07484802431610942</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>0.1748876495749635</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AC37" t="n">
         <v>0.1121295824126013</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
         <v>0.06717752234993615</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.06193806193806194</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.05487804878048781</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.0843497798972854</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.02792792792792793</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>385.122</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>377.774</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>81.5</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>18.5</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>51.06</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">  Do you need anything?  Sophia inquired quietly.  No, I'm fine.  I was just eager to discuss our former relationship, Martin replied.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.04560240719441137</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.103407936905317</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0581480911647392</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.05016918062498173</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.07684364608319648</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.04909437249700942</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.05263191309702937</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.02208103646952568</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.01528735632183908</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>1.5</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.2016730595774484</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.2597262441012441</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.1317265395894428</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.09026411567971671</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>0.1696428571428572</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.1577964828561329</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.03722993827160494</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AG38" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>393.919</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>385.162</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>89.90000000000001</v>
       </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>10.1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>33.13</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  By the way, do you have a Kit Kat on you by any chance?  What?  No, Sophia answered, looking at Martin sympathetically.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.073743432370856</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.07032958884810737</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.01754385964912281</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.032719836400818</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.040566398775354</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.06076738832897848</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.04698644058485851</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.05904573438874231</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.5</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.1004385964912281</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.1504498447155252</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1761780262050727</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.08001660619844407</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.104831984302183</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.1033840349015446</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>0.06018099547511313</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.04810996563573883</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.05243445692883895</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.046875</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.04615384615384616</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.0339622641509434</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>402.434</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>394.7</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>83.3</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>16.7</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>52.66999999999999</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  Martin felt like a new person.  That's okay.  I'll be back in a jiffy, Martin said while he jumped to find a nearby kiosk.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.001629072681704261</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.03856066791083074</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.01957251377705796</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.01951363893805991</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.007804638318784957</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.07895825427337193</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.03134717871629741</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.04871088997402256</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.02966176696753833</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.05620792771902789</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.08857023473877568</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.11510320937324</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.01590693257359924</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.01584694947538451</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.04959433865924778</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.03533212194629518</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.01193351736829998</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.0370950983557404</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.02513821860362301</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.06673490233171868</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.06461843919970976</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.06305491763023535</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.02377697677181433</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.03857091029375673</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4689,104 +5089,114 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>410.187</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>402.454</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>90</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>10</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>45.88</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">  On the way to their table, while munching what was left of the Kit Kat, Martin laughed at himself.  Why didn't I go to Andre the Giant sooner?</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.01612903225806452</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>0.03985507246376811</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>0.08985755053230886</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.1072697238067395</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.06913949275362319</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.1176361472690031</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.06400296176021769</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S41" t="n">
+      <c r="U41" t="n">
         <v>0.05043859649122807</v>
       </c>
-      <c r="T41" t="n">
+      <c r="V41" t="n">
         <v>0.1173193511387842</v>
       </c>
-      <c r="U41" t="n">
+      <c r="W41" t="n">
         <v>0.05649717514124294</v>
       </c>
-      <c r="V41" t="n">
+      <c r="X41" t="n">
         <v>0.09567028211337443</v>
       </c>
-      <c r="W41" t="n">
+      <c r="Y41" t="n">
         <v>0.05298013245033113</v>
       </c>
-      <c r="X41" t="n">
+      <c r="Z41" t="n">
         <v>0.1215658530833628</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AA41" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AB41" t="n">
         <v>0.2397372742200329</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>0.07370184254606366</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AD41" t="n">
         <v>0.1454022988505747</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>0.125</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>0.09742457689477557</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>0.08230832013058716</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AI41" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>416.988</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>410.227</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>68.8</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>16.9</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>14.2</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>10.48</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">  I must never admit this to Mom.  Martin pushed his stool with large, foolish grin on his lips.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>milkywaysynonyms_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.07829861111111111</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.07070707070707072</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.07496638278798745</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.01</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>0.02</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.0493114406779661</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.05722381448671184</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.07885370643102602</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>0.8</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.08108108108108109</v>
       </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
         <v>0.04700854700854701</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.1265756302521008</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.1519230769230769</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.1408692337018681</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.07222222222222222</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.1069456553327521</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
